--- a/wk3/DAB_Excel_Charts_Master_Class.xlsx
+++ b/wk3/DAB_Excel_Charts_Master_Class.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\Instructor_material\inst-dab-sep-26\wk3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jatin/Desktop/Learnings/Upright/Student_Repo/wk3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF7ED8F-9095-4FA2-9BAC-DF8EF51676B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA05A640-AB1C-1842-90DF-C8A9C30CA057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-4580" windowWidth="38400" windowHeight="21000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Column Chart" sheetId="1" r:id="rId1"/>
@@ -1844,6 +1844,551 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'6. Scatter Plot'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>New Customers</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="9525" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'6. Scatter Plot'!$A$2:$A$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>800</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'6. Scatter Plot'!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>102</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>115</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A10D-C74C-9BFF-76E17BE9B55C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="r"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2084690047"/>
+        <c:axId val="2064658239"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2084690047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Investment</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2064658239"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2064658239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>new leads</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2084690047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="110"/>
     </mc:Choice>
     <mc:Fallback>
@@ -2010,6 +2555,566 @@
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="241">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2225,6 +3330,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{023F755D-D40B-B54B-2737-D7D398FD7DE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2550,12 +3691,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2569,7 +3710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2583,7 +3724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2597,7 +3738,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2611,7 +3752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2625,7 +3766,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2639,7 +3780,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2659,12 +3800,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -2678,7 +3819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2692,7 +3833,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -2706,7 +3847,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -2720,7 +3861,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2734,7 +3875,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -2748,7 +3889,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -2759,7 +3900,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2770,7 +3911,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -2781,7 +3922,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2792,7 +3933,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2803,7 +3944,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -2814,7 +3955,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2834,12 +3975,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -2850,7 +3991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -2861,7 +4002,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -2872,7 +4013,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -2883,7 +4024,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -2894,7 +4035,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>43</v>
       </c>
@@ -2914,12 +4055,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2933,7 +4074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2947,7 +4088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2961,7 +4102,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2975,7 +4116,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2989,7 +4130,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3003,7 +4144,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3023,12 +4164,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -3042,7 +4183,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3056,7 +4197,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -3070,7 +4211,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -3084,7 +4225,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -3098,7 +4239,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -3112,7 +4253,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -3123,7 +4264,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -3134,7 +4275,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -3145,7 +4286,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -3156,7 +4297,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -3167,7 +4308,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -3178,7 +4319,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -3198,9 +4339,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>53</v>
       </c>
@@ -3208,7 +4349,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>100</v>
       </c>
@@ -3219,7 +4360,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>200</v>
       </c>
@@ -3230,7 +4371,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>300</v>
       </c>
@@ -3241,7 +4382,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>400</v>
       </c>
@@ -3252,7 +4393,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>500</v>
       </c>
@@ -3263,7 +4404,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>600</v>
       </c>
@@ -3271,7 +4412,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>700</v>
       </c>
@@ -3279,7 +4420,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>800</v>
       </c>
@@ -3296,12 +4437,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
@@ -3312,7 +4453,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -3323,7 +4464,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -3334,7 +4475,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -3345,7 +4486,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -3356,7 +4497,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>41</v>
       </c>
